--- a/Forkin-finding-2014-phi4-mini-bert-scores.xlsx
+++ b/Forkin-finding-2014-phi4-mini-bert-scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>DOCUMENT</t>
   </si>
@@ -73,6 +73,18 @@
     <t>Summarize the coroner’s findings in 2-3 sentences</t>
   </si>
   <si>
+    <t>Did the coroner make recommendations for future prevention? If yes, what were they?</t>
+  </si>
+  <si>
+    <t>Differentiate between the immediate cause of death and contributing factors.</t>
+  </si>
+  <si>
+    <t>Did the coroner evaluate the adequacy of supervision, treatment, or care provided? Explain the conclusion.</t>
+  </si>
+  <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
+  </si>
+  <si>
     <t>The deceased was Luke Isaac Forkin, born in Western Australia on 23 October 1982 (page 4)</t>
   </si>
   <si>
@@ -106,79 +118,131 @@
     <t>The coroner found that Luke Forkin committed suicide by hanging while absent without leave from Graylands Hospital. The care, treatment, and supervision were reasonable and appropriate, and the decision to grant unescorted ground access was justified by his apparent stability (pages 20–21).</t>
   </si>
   <si>
-    <t>The provided text does not contain explicit personal identifying details (like name) about "the deceased." Therefore it is impossible to determine who specifically they refer to based on this given contextual data alone. More specific references or context would be needed for an accurate identification of the individual being referred as 'the deceased'. 
-However, if there was a preceding paragraph in Ex 1 that mentioned someone's full name and these details are missing from what has been provided here (e.g., mentioning "John Doe" earlier), then it could help identify who is meant by this description. But with just context information given above about the individual's background without any direct naming, it's not possible to pinpoint exactly whom 'the deceased' refers to.
-Therefore based on available data:
-Answer: The name of ‘the deceased’ cannot be determined from provided text alone as specific identifying details (like full personal names) are missing. More contextual or preceding information would help in accurate identification.</t>
-  </si>
-  <si>
-    <t>The specific date of when events leading up to Mr Ward's discovery are mentioned is November 29th or October 31st depending on which year's event you refer to. However, for this context related specifically about Mr and Ms Ward leaving at 6:30am the next morning after noticing that someone had died (which would be December first) it's implied they left home early in their usual routine.
-Considering events leading up:
-- The deceased was discovered hung by his neck with an electrical cord tied to a rafter.
-- Ambulance paramedics arrived and noted no signs of life shortly afterward. A Life Extinct Form is usually completed when there's absolutely confirmed death after unsuccessful resuscitation efforts, which in this case took place within minutes (i.e., around 4:10pm).
-So the exact moment they discovered he was dead could be any time between Mr Ward's return home and paramedics arriving but closely tied to what occurred that day.
-Thus:
-**Answer:** The death likely happened on December first of unspecified year, assuming no prior knowledge about which specific date or years context refers. Exact hour not stated in the given snippets around 4:10pm upon their arrival back at house after noting deceased hanging from electrical cord hung by neck and tied to rafter through open manhole ceiling.
-**Refined Answer for death occurrence:** December first (specific year unspecified), possibly between discovering incident time post-departure home.</t>
-  </si>
-  <si>
-    <t>The location where Luke Isaac Forkin died is 33A Snowbird Gardens, Joondalup.</t>
+    <t>Yes. The coroner noted that Dr. Nathan Gibson (Chief Psychiatrist) had initiated development of a Mental Health Act orientation and training program for all consultant psychiatrists to clarify the legal requirements for detaining and treating patients with personality disorders (page 20).</t>
+  </si>
+  <si>
+    <t>Immediate cause: Ligature compression of the neck (hanging) (page 14). Contributing factors: Substance abuse, personality disorder, pending court case, strained relationship with his mother, and recent absconding from psychiatric care (pages 9–13, 20)</t>
+  </si>
+  <si>
+    <t>Yes. The coroner concluded that Graylands Hospital staff provided reasonable and appropriate treatment and supervision. Although there were minor issues with record-keeping and a 45-minute delay in declaring him AWOL, these were not contributory to the death. Staff acted under the “least restrictive” principle of care (pages 15–17).</t>
+  </si>
+  <si>
+    <t>Yes. The case highlights the complex challenges in managing patients with personality and substance-use disorders and the need for clearer guidance under the Mental Health Act. It also emphasized system improvements in record-keeping, risk assessment, and staff training, which were implemented after the inquest (pages 18–20)</t>
+  </si>
+  <si>
+    <t>Answer: The deceased is a male born in Western Australia on 23 October 1982 into a blended family consisting of his mother who had four children from three relationships. His elder sibling Jason came from her first relationship and he took his surname, while younger siblings were from subsequent partners.
+Additional context reveals the following:
+1. At birth when their father was imprisoned for serious offenses.
+2. The deceased suffered severe injuries due to an accidental gunshot wound by step-father in 2002 which led him to receive Disability Support Pension but also substantial compensation payments as a result of his injury (lost third part of pancreas, kidney damage and fractured vertebrae).
+3. He had used drugs like amphetamines daily for five years starting from age around mid-twenties.
+4. The deceased engaged in drug-related offenses including burglary to fund the purchase or use of substances which include cannabis, heroin, LSD, ecstasy (though it's unclear whether he abused alcohol as well).</t>
+  </si>
+  <si>
+    <t>The date of death cannot be determined from the provided text as there is no specific mention or reference to a precise time when Mr Ward saw his deceased friend hanging by an electrical cord. The last confirmed event related to seeing someone was at 12.OOam/1.OOpm on November 29, 2010; however, it does not indicate that this person died during the described events.
+If we assume "the day" in line with other contexts refers explicitly to a particular date mentioned earlier (November 29), then Mr Ward saw his friend hanging by an electrical cord at approximately noon/1 PM on November 30. However, without further information about how long it took for him or others after the sighting of this incident before they observed that there were no signs left alive upon their arrival to help them, we cannot deduce a specific date and time when death occurred.
+Given these constraints:
+Answer: The precise moment of Mr Ward's friend's passing is not provided in your context. He was found hanging at approximately noon/1 PM on November 30 after being seen by Mrs. Ward earlier that day (November 29). Further details would be needed to pinpoint the exact time and date he ceased breathing or died, but this information does not appear within the given text snippet.</t>
+  </si>
+  <si>
+    <t>The death occurred on 30 November 2010 at Snowbird Gardens, Joondalup.</t>
   </si>
   <si>
     <t>The cause of death is ligature compression (hanging).</t>
   </si>
   <si>
-    <t>The given context does not explicitly mention who is serving as the Presiding Coroner. Ms M. Smith assisted by Ms R Hartley (State Solicitors Office) appears to be acting on behalf of a department rather than holding an official role related directly with being the Presiding Coroner for this particular case under review.
-To answer your query correctly, based solely on context information provided:
-Answer: The presiding coroner is not explicitly mentioned in given text.</t>
-  </si>
-  <si>
-    <t>The events that led up to Mr Ward's deceased son coming home in a distressed state are as follows:
-1. On 2 December 2010 (presumably during his lunch break), an argument broke out between him and Ms Ward, which unfortunately turned violent.
-2. During this altercation with Ms Ward at their residence located on King Street in Kwinnepin Parkland West, Mr Ward struck her head against the wall causing significant injuries to both of them; however, no other severe physical damage was inflicted upon either party during or after that incident.
-The deceased's father and mother then left for work early one morning (6.30am), assuming their son was still asleep at home because he did not see him before leaving.
-Unfortunately due to a prior unresolved issue between Mr Ward &amp; Ms Ward, they forgot to lock the front door of his house upon exiting; as it turned out that night while returning from school around 4pm when things unexpectedly took an unfortunate turn for them all. They were shocked and distressed at what happened afterwards.
-They called emergency services (000) after discovering their son's tragic death: Mr Ward cut through a wire attached to the deceased son in order to free his neck, then he applied chest compressions using hands while waiting for paramedics' arrival; unfortunately despite these attempts there was no response indicating that they had lost any signs of life.
-The ambulance arrived shortly thereafter and found him unresponsive. Paramedics performed CPR on their son's body whilst transporting them back home where a Life Extinct Form by one of the medic's was completed, confirming his death as being without hope for revival.
-An autopsy conducted after Mr Ward returned from work revealed that he had suffered ligature-type damage to skin around neck area and fracture in main cartilage present within throat (a consequence due to strangulation); lungs were congested resulting from lack oxygen. Additionally toxicology analysis showed the presence of prescription drugs, sub therapeutic levels cannabis compounds as well as low level tetrahydrocannabinol indicating recent use; therefore it is believed that Mr Ward was under influence during this fatal incident.
-Ultimately I concluded his cause and manner death to be suicide by hanging using an electric cord wrapped around neck area. This conclusion came after examining all available evidence provided including toxicology results, the autopsy report as well as other related information gathered about him prior.
-In summary: After leaving for work in a rushed state due to unresolved issues with Ms Ward that morning; Mr Ward returned home and discovered his son hung by an electric cord tied around neck area through manhole located within ceiling. He managed only cut it using hands before paramedics arrived who tried resuscitation efforts but unfortunately could not revive him.
-I find that the circumstances leading up to this tragic death were due to a combination of unresolved interpersonal issues between Mr Ward and Ms Ward, neglect in securing door lock as they left for work earlier than usual; ultimately culminating into their son taking his own life by hanging himself using an electric wire around neck area. This is also further supported through toxicology results showing drugs/heroin/LSD/ecstasy presence which may have affected the deceased's judgement or mental stability during this incident leading up to suicide attempt.
-I find: cause of death was ligature compression on Mr Ward son's neck, and manner of death as being a self-inflicted act (suicide).</t>
-  </si>
-  <si>
-    <t>Based on the provided contextual background regarding the decedent's past:
-- The individual had a principal diagnosis of psychotic symptoms linked to schizophrenia.
-- They also suffered from drug withdrawal issues in 2005, specifically following amphetamine use and intravenous (IV) amphetamine consumption which led them into mental health care facilities multiple times. This included being admitted at Joondalup Mental Health Unit twice for related reasons: once after self-harm involving the ingestion of an unspecified substance on May 2nd or possibly April 29th, given there are discrepancies in dates mentioned (possibly due to transcription errors) and again two days later specifically citing amphetamine use.
-- On June 21st, a separate admission was made at Broome Health Service where they sought help for paranoid psychotic episodes intensified by substance abuse. The deceased received treatment with olanzapine while involuntarily hospitalized in Graylands on the following day (June 22nd).
-- By July 3rd of that year and onwards until November, there were ongoing concerns about self-harm or suicide attempts linked to amphetamine-induced psychosis.
-- In addition to these instances related directly back by a few months prior; another significant episode occurred in April/May where the deceased suffered from auditory hallucinations as well.
-Overall summary: The decedent had severe mental health issues connected with schizophrenia and drug withdrawal, specifically involving repeated episodes of self-harm linked primarily but not exclusively (as there are several overlapping diagnoses) to amphetamine-induced psychosis. This history involved multiple hospitalizations over a few years for psychiatric treatment in various facilities including secure wards due to the risk posed by their own behaviors or substance abuse issues exacerbating mental health conditions.</t>
-  </si>
-  <si>
-    <t>Based on the provided text about an inquest into deaths at Graylands mental health facility held before Coroner DH. Mulligan:
-- The specific individuals who testified are referred to as "deceased persons" and others whose names have not been disclosed.
-As for assistance, it is mentioned that there was evidence adduced related to general systemic issues pertinent to the institution (Graylands), which implies testimony from professionals or experts knowledgeable about Graylands' conditions. This could include:
-- Staff members of Graylands who provided insights into supervision and care quality at their facility.
-Without explicit names in this summary, it's impossible for me as an AI with a knowledge cutoff date up until 2023 to accurately provide specific individuals’ identities involved directly unless they were mentioned within the text you have shared. However, interested parties present during Coroner Mulligan's original inquiries or those invited by Acting State Coroner Evelyn Vicker (such as medical professionals linked to Graylands) likely provided testimony and assistance.
-To obtain a complete list of witnesses who testified in this particular case would require access to full transcripts from the court records that are beyond my current capabilities. The details about all individuals involved can only be found within those official documents, which typically include lists or summaries with names for reference purposes following legal procedures after an inquiry concludes.</t>
-  </si>
-  <si>
-    <t>Yes, Luke Isaac Forkin was considered a "person held in care" under Section 22 (1)a) of the Coroners Act at the time of his death. This status applied because he died as an involuntary patient while absent without leave from Graylands Hospital and thus fell within that provision's definition for mandatory coroner investigation into deaths appearing to be Western Australian when such a person was "immediately before" their death held in care under Section 3 of the Coroners Act.
-Answer: Yes</t>
-  </si>
-  <si>
-    <t>Yes, according to Ex 1, Vol 1, Tab 8 (39), a toxicology analysis revealed therapeutic levels along with sub-therapeutic amounts of prescription medicines and low concentrations of tetrahydrocannabinol—a substance derived from cannabis—which indicated that there was the use of marijuana within approximately one day prior to death. This suggests evidence for recent consumption or presence of drugs in Mr. Graylands' body at a time close to his passing.
-The toxicology findings can be summarized as follows: There were therapeutic and sub-therapeutic levels present, indicating adequate but possibly insufficient dosing with prescription medications; low level tetrahydrocannabinol was detected suggesting the recent use (within 24 hours) of cannabis.</t>
-  </si>
-  <si>
-    <t>The coroner addressed issues related to each death separately but also considered how systemic problems at Graylands may have influenced these deaths. The examination included evaluating whether deficiencies such as inadequate building conditions affected patient care and treatment quality for mental illnesses, although many general evidence points were deemed not sufficiently connected with all the respective deaths under Section 25 of the Coroners Act 1996 to comment on them specifically in relation to each death investigated by this inquiry.
-The context also suggests that there was an investigation into whether systemic issues at Graylands influenced patient treatment and care quality. Evidence related to general or systematic problems pertinent to Graylands, such as building conditions affecting mental health patients' environments for therapeutic purposes (not all connections with deaths being explored due to Section 25 limitations), were considered in understanding the broader context of each death investigated.
-Furthermore, Ms M Smith assisted Mr Coroner R Hartley from State Solicitors Office representing Health Department WA. It implies that legal counsel was involved and there might have been a focus on public health implications for mental illness treatment at Graylands hospital facilities as related to patient deaths under investigation by the coroner's office. Overall findings seem focused primarily around individual cases with broader systemic issues acknowledged but not fully connected due to specified statutory limitations in commenting upon them directly.
-In summary, while general and systematic problems pertinent to Graylands were considered for their potential bearing on death investigations during this inquiry led by Coroner R Hartley assisted by Ms M Smith (State Solicitors Office representing Health Department WA), many of those issues could not be specifically linked under Section 25 with individual deaths investigated. Legal counsel's presence suggests there was an investigation into broader systemic failures impacting patient care quality and treatment at Graylands, particularly concerning mental health patients' environments affecting therapeutic outcomes.
-Key Points:
-- Coroner R Hartley conducted the inquiry focusing on specific cases due to limitations set by s.25.
-- Systemic issues were considered but not linked directly with individual deaths under investigation in this context; legal counsel's involvement implies public interest and broader systemic failures implications at Graylands for mental health patient care quality, highlighting a focus possibly beyond just death inquiries (e.g., therapeutic outcomes related building conditions) as per Ms M Smith’s assistance.</t>
+    <t>The Presiding Coroner is Ms. R Hartley (State Solicitors Office).</t>
+  </si>
+  <si>
+    <t>The events that led up to Mr Ward's wife's (Ms) death include her coming home from work at 4 PM one particular afternoon in December. She discovered a locked front door upon arrival but entered through an open manhole instead of using it as she usually would, since this was not the first time things had been like this.
+Upon entering and seeing his wife hanging by an electrical cord tied to some sort of fixture (presumably from her work-related tasks or household activities), Mr Ward realized something was seriously wrong. He immediately called emergency services for help but also took action himself; he cut off the electric wire that seemed responsible for strangling Ms, performed CPR on Mrs with chest compressions until paramedics arrived.
+When ambulance personnel reached them and assessed their situation at around 4:10 PM (as indicated by a Life Extinct Form being completed shortly before this time), they found no signs of life in his wife. Given these circumstances—particularly the presence of ligature-type marks on her neck, internal injuries consistent with strangulation like fractures to major throat cartilage without any other apparent physical trauma—it was concluded that Mrs Ward's cause and manner of death were due to asphyxiation from hanging (ligature compression) which Mr. Ward classified in his findings simply by stating "I find."
+These details point directly toward a tragic self-inflicted accident where Ms. Ward likely became entangled with an electrical cord or similar object, leading ultimately to her own strangulation and death at the hands of circumstances that she herself had put into motion—at least as described up until Mr. Ward's intervention.
+It is important for mental health professionals dealing in such cases (as mentioned by Dr Cooke) because prior conditions like Ms' drug use or any other pre-existing trauma may significantly affect both investigation outcomes and subsequent psychiatric evaluations of her intent to commit suicide, among others factors related not just with direct causation but also the broader context surrounding it.
+Therefore, summarizing: Mrs Ward became entangled in an electrical cord tied by accident during a routine activity. Realization prompted Mr. Ward's immediate intervention (cutting off electricity and CPR) before paramedics confirmed no life signs—leading to her death being classified as accidental homicide through strangulation via hanging-related ligature compression of the neck.
+This incident, although unfortunate due to its fatal outcome that led directly into an emergency medical context culminating in a classification concerning Mr. Ward's wife’s demise by suicide (as per his findings), also opens up conversations around mental health challenges possibly exacerbated or influenced significantly through years-long substance use and related traumatic experiences noted earlier within her life history, which must be accounted for deeply during any comprehensive examination of the tragic event as well its ramifications on family members including Mr. Ward himself.
+This narrative is reflective strictly from available information; it's crucial to remember that personal stories behind such events often carry deeper context with varied impacts requiring sensitive and thorough exploration especially in legal scenarios where clarity around intentions (or lack thereof) plays a paramount role amidst tragedy-induced outcomes as seen here leading toward finality via unfortunate accident during otherwise routine circumstances.</t>
+  </si>
+  <si>
+    <t>The deceased had a significant psychiatric illness involving psychotic symptoms consistent with schizophrenia that was initially diagnosed after experiencing suicidal self-harm coupled with auditory hallucinations. These events led to his admission into Joondalup Mental Health Unit in 2005, and he underwent treatment there before being discharged.
+He also experienced episodes of paranoia linked directly to amphetamine use; specifically mentioned were instances involving intravenous (IV) amphetamines which contributed substantially to the exacerbation of psychotic symptoms. This pattern indicates a strong connection between his substance abuse issues—particularly IV amphetamine—and mental health deterioration, as evidenced by repeated hospital admissions.
+In 2006 and later in November 2007, there was an admission into Broome Health Service followed closely with hospitalization at Graylands Mental Health Services after he sought assistance from police following suicidal behavior. His psychiatric condition during this period included paranoid psychotic episodes that were again linked to substance abuse—this time IV amphetamine use.
+Overall, his mental health history includes chronic schizophrenia and acute exacerbations related directly or indirectly (through drug withdrawal in 2005) to the consumption of various substances including but not limited to psychoactive drugs. His treatment regimen over these times included medications such as olanzapine—a common antipsychotic medication—and he was placed involuntarily into secure wards due to his unstable condition, especially during episodes where suicidal ideation or behavior were present.</t>
+  </si>
+  <si>
+    <t>Based on the provided context:
+The individuals who testified specifically related to two deceased persons were mentioned as giving evidence during particular dates (20th March 2013 through April). Additionally, there is mention of "interested parties" invited by Acting State Coroner Evelyn Vicker. These interested or involved entities could include family members of those affected.
+However, specific names and roles are not provided within the context given for individuals who testified in relation to all nine deceased persons at Graylands nor details on how many people attended as witnesses during these hearings beyond "interested parties." Therefore:
+Answer: The text does mention that evidence was adduced related specifically to two of a total number unspecified. Furthermore, it states 'all interested or involved entities' were invited by Acting State Coroner Evelyn Vicker; however, no specific names are given within this context for individuals who testified at the inquest.
+For accurate details including full names and roles (e.g., family members as witnesses), we would need to refer back directly to transcripts of these hearings. This document only provides an overview rather than detailed accounts or lists individual participants by name unless those records were provided separately from what was summarized here.</t>
+  </si>
+  <si>
+    <t>Yes, according to Section 22 (1)a) of the Coroners Act 1996 as mentioned within your provided text, Luke Isaac Forkin was indeed classified and thus deemed "a person held in care" at Graylands Hospital prior to his death. This classification triggered a mandatory requirement for an inquest into his passing by virtue that he died while being treated there under Section 3 of the Coroners Act 1996 as per subsection (1) outlined above, confirming Luke Isaac Forkin's status relevantly within your given context information.</t>
+  </si>
+  <si>
+    <t>Yes, according to Ex 1 Vol 1 Tab 8 (Entry No 39), a toxicology analysis was conducted on substances found within the deceased's system. The results indicated therapeutic and subtherapeutic levels of prescription medications as well as low-level tetrahydrocannabinol—a compound associated with cannabis use—suggesting that there had been consumption or presence of these drugs in their body just prior to death.
+The summary would be: Evidence from toxicology analysis showed the deceased was under medication at therapeutic and below-average doses, along with traces indicative of recent (within 24 hours) ingestion of tetrahydrocannabinol.</t>
+  </si>
+  <si>
+    <t>The court concluded that while numerous systemic issues were identified at Graylands concerning mental healthcare conditions such as building maintenance or therapeutic environments for patients with severe personality disorders suffering from psychosis and depression (such as Mr. A, Ms B., Mrs C etc.), they did not directly pertain to the deaths in question; however it was found upon examination of individual cases that some aspects related specifically to a lack of adequate supervision by staff during suicide attempts were connected indirectly through negligent failure to properly supervise patients prone to violence or suicidal ideation as per s. 25 Coroners Act, thereby warranting further investigation into these matters and implications on the quality of patient care at Graylands facilities. The court recommended that any findings relating directly with causative factors in each specific death be investigated separately under Section 14(1) (C) which applies to mental patients who had committed suicide or died due to a severe personality disorder coupled with psychosis, depression and suicidal tendencies. Furthermore it was found upon examination of Mr A's case specifically that there were deficiencies related directly to the supervision by staff during Ms B.'s suicide attempt in her room at Graylands Hospital; however this lack did not necessarily constitute causative factors pertaining solely or predominantly as a contributory factor for his death, but rather an example demonstrating negligent failure on behalf of hospital management under Section 25 Coroners Act. Therefore it was deemed appropriate to investigate the circumstances surrounding Mr A's suicide attempt in order to identify any direct causal links between Ms B.'s actions (such as her suicidal ideation and depression) along with lack of adequate supervision by staff during his attempted recovery at Graylands Hospital which may have contributed towards causing or exacerbating existing factors leading up to such events. This would further assist the coroner upon investigation into whether there were deficiencies related directly in regards to Ms B's subsequent suicide attempt following her release from hospital after Mr A’s death; as well allow a determination of any potential causative links for either case under Section 25 Coroners Act which applies specifically regarding mental patients who had committed or died due to severe personality disorder, psychosis and depression. Ultimately this investigation would aid in establishing an appropriate conclusion on whether deficiencies relating directly pertaining solely/more predominantly caused Mr A's suicide attempt along with subsequent cause of death; as well provide insights into necessary measures that should be taken by hospital management/supervisory staff at Graylands Hospital to prevent such circumstances from occurring again.
+Overall the court findings concluded there were systemic issues present within mental health facilities in terms of inadequate supervision, treatment and care for patients prone to suicidal ideation coupled with severe personality disorder; however while those deficiencies may have indirectly contributed towards causing or exacerbating existing factors leading up to events concerning suicide attempts at Graylands Hospital they did not directly pertain solely/more predominantly as causative factor(s) contributing significantly in regards to Mr A's death. Therefore further investigation was deemed necessary under Section 14(1)(C), specifically pertaining exclusively/singlely/most dominantly towards causes relating only/or more than half of the reasons for any specific person’s suicide attempt; or their subsequent cause (death). This would aid a better understanding in regards to causative links between patient conditions, circumstances surrounding his/her death and deficiencies that may exist within Graylands Hospital's treatment facilities. The court recommended further investigation into Ms B.'s case following her release from hospital after Mr A’ death due to similarities regarding inadequate supervision by staff during suicide attempt as well as mental health concerns shared among both patients; however this was deemed not directly pertinent solely/more predominantly in regards with causative factors of his/her subsequent cause (death).
+The court findings therefore concluded it would be appropriate for the investigation into deficiencies relating specifically and/or exclusively/singlely/most dominantly pertaining to Mr A’s suicide attempt along as well any deficiency related that may have contributed significantly towards causing or exacerbating existing circumstances leading up to death; but not necessarily directly connected with Ms B.'s case. This conclusion was reached due primarily in regards of whether deficiencies relating solely/more predominantly caused, were responsible for and/or played a significant role specifically/singlely/most dominantly as causative factor(s) contributing significantly towards Mr A's suicide attempt along his subsequent cause (death). Overall the court findings concluded that there are certain systemic issues present within mental health facilities; however while those deficiencies may have indirectly contributed to causing/exacerbating existing factors leading up events concerning patients’ suicides attempts at Graylands Hospital they did not directly pertain solely/more predominantly as causative factor(s) contributing significantly in regards of Mr A's subsequent cause (death). Further investigation was deemed necessary under Section 14(1)(C), specifically pertaining exclusively/singlely/most dominantly to causes relating only/or more than half reasons for any specific person’s suicide attempt; or their subsequently occurring death. This would aid a better understanding regarding causative links between patient conditions, circumstances surrounding his/her cause of (death) and deficiencies that may exist within Graylands Hospital's treatment facilities. The court recommended further investigation into Ms B.'s case following her release from hospital after Mr A’ death due to similarities pertaining in regards of inadequate supervision by staff during suicide attempt as well as mental health concerns shared among both patients; however this was deemed not directly pertinent solely/more predominantly concerning causative factors (death).
+Overall the court findings concluded it would be appropriate for investigation into deficiencies relating specifically and/or exclusively/singlely/most dominantly pertaining to Mr A’s subsequent cause of death along with Ms B's suicide attempt due to similarities regarding insufficient supervision by hospital staff during her attempts; however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. It should also be noted, deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent suicide attempt along with Ms B’s respective attempts are deemed not particularly significant or predominantly influential in regards of causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Furthermore the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily due in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall, the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides.
+Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Furthermore the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusively/singlely/most dominantly pertaining to Mr A's subsequent cause (death); however this conclusion was reached primarily in regards that whether those deficiency were directly related as causative factor(s) contributing significantly towards causing/exacerbating existing circumstances leading up events concerning patient's suicides. Overall the court findings concluded it would be appropriate for investigation into deficiencies relating exclusi</t>
+  </si>
+  <si>
+    <t>Based on the provided text alone from which to infer whether a recommendation was made or identify any specific measures suggested by Coroner Smith, it appears that there is no direct indication given in this excerpt about particular preventive actions being recommended. The introduction states:
+"Rather... I have addressed them [issues related to Graylands] not separately but as part of the broader context."
+This suggests an intention from Mr. Justice Smith's perspective was more thematic and integrative, discussing systemic issues broadly rather than prescribing specific future measures.
+For a comprehensive answer regarding Coroner recommendations for prevention based on this excerpt alone would require additional information beyond what is provided here (i.e., sections following paragraph 12 or further details that may not be included in the text above).</t>
+  </si>
+  <si>
+    <t>Based on the provided contextual excerpts from an investigation report into Mr. Ward's case:
+**Immediate Cause of Death:**  
+The primary reason for his demise is clearly identified as ligature compression (hanging) caused by a knot tied around Mrs. Ward’s neck with electrical cord, which led to significant trauma and damage.
+Specifically mentioned:
+- The post-mortem examination revealed "ligature-type marking" on the skin of Mr. Ward's neck.
+- Internal injuries included fracture in main throat cartilage due to compression from ligation by a knot tied around his neck using an electric extension lead (Ex 1, Vol 2, Tab 51).
+- Congestion observed during post-mortem examination consistent with asphyxiation through the compressed cervical airway.
+**Contributing Factors:**  
+The contributing factors are those that may have played roles in leading up to and possibly exacerbating Mr. Ward's death but were not directly responsible for it:
+1. **Unintentional Ingestion of Alcohol:**
+   - Toxicology results showed "sub-therapeutic levels" indicating alcohol consumption was present (Ex 1, Vol 2, Tab 51).
+2. **Use of Substances within the Last Day Prior to Death:** 
+   - Found low level tetrahydrocannabinol in toxicology analysis indicative that cannabis had been consumed recently.
+3. **Circumstantial Factors:**
+   - The deceased left his house unlocked which could have made him more accessible.
+   - Mr. Ward and Ms. Ward did not see the deceased initially, assuming he was still asleep at home (Ex 1 Vol 2 Tab 51).
+4. **Mental Health Issues:** 
+While there is no direct mention of psychiatric evaluation or mental health issues from this provided context alone; given that self-harm cases sometimes hint towards underlying psychological distress and need for comprehensive assessment beyond the physical evidence presented here.
+The immediate cause (ligature compression) directly led to Mr. Ward's death through asphyxiation by neck ligation, while various contributing factors outlined above influenced circumstances surrounding his untimely demise but were not direct causes of this fatal incident themselves.</t>
+  </si>
+  <si>
+    <t>Yes, based on the given passage from an inquest report under the Coroners Act 1996:
+The coroner evaluated whether there were any deficiencies concerning how deceased patients at Graylands hospital received their supervisory duties and quality of mental health services. The context information suggests that multiple aspects related to supervision or treatment for mentally ill individuals within a specific healthcare setting, which may have had relevance due to systemic issues.
+In this case study:
+- There was evidence provided regarding general conditions such as the state-of-the-art wards at Graylands hospital.
+- Generalized testimony about environmental factors and staff considerations were included in relation to mental health care quality but not specifically tied enough directly into all deaths for individual comment under Section 25 of the Coroners Act.
+However, there is a detailed analysis provided concerning:
+1. The deceased individual's behavior: Nursing staff reported that this person was no longer belligerent or aggressive.
+2. Risk assessments performed by Dr Rosell and another doctor (unnamed in context), indicating low risk for self-harm with respect to the individual under their care.
+From these specific examples, it's evident there is an evaluation of certain aspects relating directly:
+- The decisions made regarding unescorted ground access based on a considered judgment that this approach was necessary given his condition and impulsivity.
+- A professional assessment confirming minimal risks related to self-harm or absconding when granting such privileges.
+The conclusion drawn by the coroner, from these evaluations provided within context (but not explicitly spelled out in full), appears as follows:
+There is no reasonable basis for criticism of any risk assessments conducted concerning this deceased individual's behavior and mental health. Thus it can be concluded that based on presented evidence at least some parts about supervision or care are considered adequate under Section 25 criteria, with particular emphasis placed upon the treatment decisions reflecting an approach tailored to specific individual needs rather than a broadly restrictive method.
+In summary:
+- The coroner did evaluate certain aspects of supervisory duties and quality mental health services.
+- Specific evaluations related directly to behavior risk assessments were deemed satisfactory by professional standards.</t>
+  </si>
+  <si>
+    <t>Yes, based on the provided excerpts from an inquest into deaths at Graylands mental health institution (Graylands), there are several themes that emerge which could be seen as indicative of larger issues related to systemic problems within healthcare institutions and their impact on patient treatment outcomes. Here is a breakdown:
+1. **Building Conditions**: The evidence about poor building conditions was presented not just for the specific cases at Graylands but also in relation to broader concerns regarding whether outdated facilities contribute negatively towards therapeutic environments, potentially affecting patients' mental health.
+2. **Systemic Issues and Supervision Quality**: There is mention of systemic issues pertinent to general or institutional care that may have influenced patient outcomes—a reminder about how individual incidents can be symptomatic of larger structural problems within healthcare institutions such as Graylands in this context.
+3. **Risk Assessment Failures**: The suicide risk-assessment before granting the deceased unescorted ground access highlights potential flaws and oversights related to assessing risks, which could point towards a broader need for improvement across mental health facilities when it comes to patient safety protocols concerning suicidal ideation or intent of absconding.
+4. **Delayed Response in Critical Situations**: The delay after declaring someone AWOL (absent without leave) points toward the necessity of having effective and timely communication channels within institutions, especially regarding patients with a history that may suggest they are at higher risk for harm to themselves due to their actions or behaviors while absconding.
+5. **Record-Keeping Issues**: The lack of proper record-keeping concerning ground access suggests broader issues related to documentation protocols in healthcare settings which could have direct implications on patient monitoring, continuity of care and safety procedures enforcement as well as accountability measures within the institution's staff practices.
+These themes suggest that while there might be isolated incidents or individual cases at Graylands resulting in tragic outcomes like deaths under investigation by an Inquest jury, they also seem to reflect larger systemic issues. Lessons drawn from this context would involve acknowledging patterns of inadequate facility maintenance impacting patient health and safety (building conditions), recognizing the need for improved risk assessment procedures regarding suicide prevention within mental healthcare institutions as well as robust record-keeping mechanisms in place.
+Overall, these broader lessons are certainly relevant not only directly to public safety but also broadly inform institutional care practices across various sectors. The highlighted patterns underscore an essential dialogue about standards of patient treatment and institution accountability which can help prevent future tragedies similar to those at Graylands by prompting systemic change as opposed solely focusing on individual failures or missteps in healthcare settings.</t>
   </si>
 </sst>
 </file>
@@ -536,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -570,19 +634,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>0.7617403864860535</v>
+        <v>0.7755882740020752</v>
       </c>
       <c r="F2">
-        <v>0.7939887046813965</v>
+        <v>0.881932258605957</v>
       </c>
       <c r="G2">
-        <v>0.777530312538147</v>
+        <v>0.8253488540649414</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -593,19 +657,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>0.7550408840179443</v>
+        <v>0.7706453204154968</v>
       </c>
       <c r="F3">
-        <v>0.8373062014579773</v>
+        <v>0.8590156435966492</v>
       </c>
       <c r="G3">
-        <v>0.7940484881401062</v>
+        <v>0.8124344348907471</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -616,19 +680,19 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>0.9052658677101135</v>
+        <v>0.939785361289978</v>
       </c>
       <c r="F4">
-        <v>0.9228339195251465</v>
+        <v>0.916156530380249</v>
       </c>
       <c r="G4">
-        <v>0.9139655232429504</v>
+        <v>0.9278205633163452</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -639,10 +703,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>0.9788520932197571</v>
@@ -662,19 +726,19 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>0.7918615937232971</v>
+        <v>0.8572604656219482</v>
       </c>
       <c r="F6">
-        <v>0.8506621718406677</v>
+        <v>0.8747215270996094</v>
       </c>
       <c r="G6">
-        <v>0.8202093839645386</v>
+        <v>0.8659029603004456</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -685,19 +749,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>0.7780340909957886</v>
+        <v>0.7800989151000977</v>
       </c>
       <c r="F7">
-        <v>0.8323461413383484</v>
+        <v>0.8269121646881104</v>
       </c>
       <c r="G7">
-        <v>0.8042742609977722</v>
+        <v>0.8028237223625183</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -708,19 +772,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>0.8037615418434143</v>
+        <v>0.8131982088088989</v>
       </c>
       <c r="F8">
-        <v>0.8584038615226746</v>
+        <v>0.8589251041412354</v>
       </c>
       <c r="G8">
-        <v>0.8301845192909241</v>
+        <v>0.8354364633560181</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -731,19 +795,19 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E9">
-        <v>0.7935233116149902</v>
+        <v>0.790180504322052</v>
       </c>
       <c r="F9">
-        <v>0.8138037919998169</v>
+        <v>0.8078149557113647</v>
       </c>
       <c r="G9">
-        <v>0.8035355806350708</v>
+        <v>0.7989003658294678</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -754,19 +818,19 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E10">
-        <v>0.8607804775238037</v>
+        <v>0.8506295084953308</v>
       </c>
       <c r="F10">
-        <v>0.9112802743911743</v>
+        <v>0.9102640151977539</v>
       </c>
       <c r="G10">
-        <v>0.8853108286857605</v>
+        <v>0.8794369101524353</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -777,19 +841,19 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E11">
-        <v>0.8804258108139038</v>
+        <v>0.8763735294342041</v>
       </c>
       <c r="F11">
-        <v>0.9269267320632935</v>
+        <v>0.9263207912445068</v>
       </c>
       <c r="G11">
-        <v>0.9030780792236328</v>
+        <v>0.9006552696228027</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -800,19 +864,111 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E12">
-        <v>0.7775090932846069</v>
+        <v>0.7784231901168823</v>
       </c>
       <c r="F12">
-        <v>0.8208488821983337</v>
+        <v>0.8335676193237305</v>
       </c>
       <c r="G12">
-        <v>0.7985914349555969</v>
+        <v>0.8050522208213806</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13">
+        <v>0.8029405474662781</v>
+      </c>
+      <c r="F13">
+        <v>0.8416187167167664</v>
+      </c>
+      <c r="G13">
+        <v>0.8218247890472412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14">
+        <v>0.7771795988082886</v>
+      </c>
+      <c r="F14">
+        <v>0.8379360437393188</v>
+      </c>
+      <c r="G14">
+        <v>0.8064150810241699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15">
+        <v>0.7954394817352295</v>
+      </c>
+      <c r="F15">
+        <v>0.8516910076141357</v>
+      </c>
+      <c r="G15">
+        <v>0.8226047158241272</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <v>0.7956656217575073</v>
+      </c>
+      <c r="F16">
+        <v>0.8502667546272278</v>
+      </c>
+      <c r="G16">
+        <v>0.8220605254173279</v>
       </c>
     </row>
   </sheetData>
